--- a/artfynd/A 7097-2020 artfynd.xlsx
+++ b/artfynd/A 7097-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7097-2020 artfynd.xlsx
+++ b/artfynd/A 7097-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2832,6 +2832,113 @@
           <t>Fladdermöss - gemensamt delprogram (biogeografisk uppföljning)</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121804887</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57373</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spånören, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589130</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6311849</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7097-2020 artfynd.xlsx
+++ b/artfynd/A 7097-2020 artfynd.xlsx
@@ -2838,7 +2838,7 @@
         <v>121804887</v>
       </c>
       <c r="B18" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
